--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/replenishmentRule.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/replenishmentRule.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="备货" sheetId="1" r:id="rId1"/>
+    <sheet name="时效 &amp; 备货" sheetId="1" r:id="rId1"/>
     <sheet name="动态备货系数" sheetId="2" r:id="rId2"/>
     <sheet name="默认日销量" sheetId="3" r:id="rId3"/>
     <sheet name="动态日销量" sheetId="4" r:id="rId4"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="96">
   <si>
     <r>
       <rPr>
@@ -125,6 +125,173 @@
     </r>
   </si>
   <si>
+    <t>备货</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>采购审批（天）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生产周期（天）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商发货（天）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>质检入库（天）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>采购频率（天）</t>
+    </r>
+  </si>
+  <si>
+    <t>物流时效（空运）</t>
+  </si>
+  <si>
+    <t>发货频率（空运)</t>
+  </si>
+  <si>
+    <t>优先级（空运)</t>
+  </si>
+  <si>
+    <t>物流时效（快递）</t>
+  </si>
+  <si>
+    <t>发货频率（快递）</t>
+  </si>
+  <si>
+    <t>优先级（快递）</t>
+  </si>
+  <si>
+    <t>物流时效（海运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（海运散装）</t>
+  </si>
+  <si>
+    <t>优先级（海运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（海运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（海运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（海运整柜)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运散装）</t>
+  </si>
+  <si>
+    <t>优先级（铁运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（铁运整柜)</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -166,170 +333,6 @@
       </rPr>
       <t>默认备货系数</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购审批（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生产周期（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商发货（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>质检入库（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购频率（天）</t>
-    </r>
-  </si>
-  <si>
-    <t>物流时效（空运）</t>
-  </si>
-  <si>
-    <t>发货频率（空运)</t>
-  </si>
-  <si>
-    <t>优先级（空运)</t>
-  </si>
-  <si>
-    <t>物流时效（快递）</t>
-  </si>
-  <si>
-    <t>发货频率（快递）</t>
-  </si>
-  <si>
-    <t>优先级（快递）</t>
-  </si>
-  <si>
-    <t>物流时效（海运散装）</t>
-  </si>
-  <si>
-    <t>发货频率（海运散装）</t>
-  </si>
-  <si>
-    <t>优先级（海运散装)</t>
-  </si>
-  <si>
-    <t>物流时效（海运整柜）</t>
-  </si>
-  <si>
-    <t>发货频率（海运整柜）</t>
-  </si>
-  <si>
-    <t>优先级（海运整柜)</t>
-  </si>
-  <si>
-    <t>物流时效（铁运散装）</t>
-  </si>
-  <si>
-    <t>发货频率（铁运散装）</t>
-  </si>
-  <si>
-    <t>优先级（铁运散装)</t>
-  </si>
-  <si>
-    <t>物流时效（铁运整柜）</t>
-  </si>
-  <si>
-    <t>发货频率（铁运整柜）</t>
-  </si>
-  <si>
-    <t>优先级（铁运整柜)</t>
   </si>
   <si>
     <t>{.platform}</t>
@@ -1381,7 +1384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1422,6 +1425,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1796,184 +1808,185 @@
       <c r="X1" s="13"/>
       <c r="Y1" s="13"/>
       <c r="Z1" s="13"/>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="AB1" s="14"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AA2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="10"/>
+      <c r="AB2" s="16" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:P1"/>
+    <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AB1:AB2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2005,39 +2018,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2080,13 +2093,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -2109,31 +2122,31 @@
       <c r="D2" s="3"/>
       <c r="E2" s="6"/>
       <c r="F2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -2143,46 +2156,46 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2233,16 +2246,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -2266,31 +2279,31 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -2300,49 +2313,49 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2386,16 +2399,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -2413,25 +2426,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2467,22 +2480,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
@@ -2500,31 +2513,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
